--- a/tests/fixtures/manual_spill_cache/input_insert_inside.xlsx
+++ b/tests/fixtures/manual_spill_cache/input_insert_inside.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31AEF5FF-80A2-4B0E-B032-5E930A735216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{633F9500-81C8-4A21-8616-E1E8B1648912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{D80C414E-81CF-488F-A66D-594C3448182B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{047B394A-E9FC-4D5B-B75E-ECB2C6BC02F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -427,7 +427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B997CE57-578B-40F2-86E7-8B25467FC671}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB22762A-CDA7-47EE-993D-D539A3FA591B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -472,7 +472,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{694B1C77-BDA4-4C5A-B62F-470F07B513E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8A011F-7E1D-49E6-8BE6-0E618A44FB3F}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
